--- a/reports/tables/comparativa_xgboost_diabetes.xlsx
+++ b/reports/tables/comparativa_xgboost_diabetes.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7202</v>
+        <v>0.7147</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>0.7531</v>
+        <v>0.7556</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0692</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2203</v>
+        <v>0.217</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3409</v>
+        <v>0.3372</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.8066</v>
+        <v>0.8055</v>
       </c>
     </row>
     <row r="3">
